--- a/data/excel/location.xlsx
+++ b/data/excel/location.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,6 +699,27 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>西柏坡</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>河北省石家庄市平山县西柏坡镇</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/excel/location.xlsx
+++ b/data/excel/location.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,6 +720,27 @@
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>莫斯科</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>俄罗斯莫斯科</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/excel/location.xlsx
+++ b/data/excel/location.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,6 +738,4048 @@
         </is>
       </c>
       <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>嘉兴</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>浙江省嘉兴市</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>南湖</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>嘉兴南湖</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>浙江省嘉兴市南湖</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>湖南省长沙市</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>湖北省武汉市</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>安源</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>江西省萍乡市安源区</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>黄埔</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>广东省广州市黄埔区</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>海丰</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>广东省汕尾市海丰县</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>江苏省南京市</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>三湾</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>江西省吉安市永新县三湾乡</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>瑞金</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>江西省赣州市瑞金市</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>于都</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>江西省赣州市于都县</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>赤水</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>贵州省遵义市赤水市</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>泸定</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>四川省甘孜州泸定县</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>会宁</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>甘肃省白银市会宁县</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>吴起</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>吴起镇</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>陕西省延安市吴起县</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>百色</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>广西壮族自治区百色市</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>宁都</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>江西省赣州市宁都县</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>遵义会议会址</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>贵州省遵义市红花岗区子尹路</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>卢沟桥</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>北京市丰台区卢沟桥</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>平型关</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>山西省忻州市繁峙县平型关</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>台儿庄</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>山东省枣庄市台儿庄区</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>南泥湾</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>陕西省延安市宝塔区南泥湾镇</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>皖南</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>安徽省南部地区</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>狼牙山</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>河北省保定市易县狼牙山</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>大别山</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>鄂豫皖三省交界的大别山区</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>孟良崮</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>山东省临沂市蒙阴县孟良崮</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>锦州</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>辽宁省锦州市</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>徐州</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>江苏省徐州市</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>香山</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>北京香山</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>北京市海淀区香山</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>天安门</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>天安门广场</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>北京市东城区天安门</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>大庆</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>黑龙江省大庆市</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>大寨</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>山西省晋中市昔阳县大寨镇</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>红旗渠</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>河南省安阳市林州市红旗渠</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>罗布泊</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区巴音郭楞州罗布泊</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>酒泉</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>甘肃省酒泉市</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>板门店</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>朝鲜半岛军事分界线板门店</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>小岗村</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>小岗</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>安徽省滁州市凤阳县小岗村</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>广东省深圳市</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>广东省珠海市</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>汕头</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>广东省汕头市</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>福建省厦门市</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>浦东</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>上海浦东</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>上海市浦东新区</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>雄安</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>雄安新区</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>河北省雄安新区</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>汶川</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>四川省阿坝州汶川县</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>兰考</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>河南省开封市兰考县</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>十八洞村</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>湖南省湘西州花垣县十八洞村</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>梁家河</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>陕西省延安市延川县梁家河村</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>古田会议会址</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>福建省龙岩市上杭县古田镇</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>通道</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>湖南省怀化市通道侗族自治县</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>黎平</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>贵州省黔东南州黎平县</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>猴场</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>贵州省黔南州瓮安县猴场镇</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>扎西</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>云南省昭通市威信县</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>苟坝</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>贵州省遵义市播州区枫香镇苟坝村</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>两河口</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>四川省阿坝州小金县两河口镇</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>沙窝</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>四川省阿坝州松潘县</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>俄界</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>甘肃省甘南州迭部县达拉乡</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>榜罗镇</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>甘肃省定西市通渭县榜罗镇</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>庐山</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>江西省九江市庐山市</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434820/index.html</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>上海浦东新区</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>东北</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>东北地区</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>中东地区</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434644/index.html</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>中原</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>中央革命根据地</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>中沙群岛</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>亚丁港</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>亚丁湾</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>亚太地区</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434761/index.html</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>亚洲地区</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434716/index.html</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>伏牛山</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434700/index.html</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>俄国</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434845/index.html</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434718/index.html</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>内蒙古自治区</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434696/index.html</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>凤阳县</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>北戴河</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>北运河</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>华中</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>华中地区</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434837/index.html</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>华北地区</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>华盛顿</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434838/index.html</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>南京长江大桥</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>南沙群岛</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>南浦大桥</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434806/index.html</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>南运河</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>台湾</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>台湾地区</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434732/index.html</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434665/index.html</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434791/index.html</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>大中城市</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>大城市</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>大清河</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>大渡河</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434811/index.html</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>太平洋地区</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434847/index.html</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>夹金山</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>子牙河</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>宁三省</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>宁冈县</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434545/index.html</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>宁夏回族自治区</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>宁都县</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434832/index.html</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>山海关</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434834/index.html</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>巴黎</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434733/index.html</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>广西壮族自治区</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434809/index.html</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434738/index.html</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>文明城市</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>新安江</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>新泽西州</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>无锡</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>日内瓦</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>旧金山</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>晋察冀边区</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>朝鲜</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>武昌</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>武汉三镇</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>武汉市</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434805/index.html</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>武汉长江大桥</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>永兴岛</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>永和市</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434658/index.html</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>永定河</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>汉阳</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434829/index.html</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>江南</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>江苏省</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>江西省</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434832/index.html</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>河北省</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434798/index.html</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>河南省</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>法国</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>泸定桥</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>洛阳</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>浙江省</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434835/index.html</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>海南岛</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>海南省</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>清川江</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434567/index.html</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>湄公河</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>湖北省</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434781/index.html</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>滨海新区</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434721/index.html</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>澎湖列岛</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>澜沧江</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>澳门</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>澳门特别行政区</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>珠海市</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434711/index.html</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434711/index.html</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>苏州工业园区</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>苏州市</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434797/index.html</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>苏联</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434820/index.html</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>西北</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>西北地区</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434727/index.html</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>西南</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>西南地区</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434555/index.html</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>西沙群岛</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>西藏自治区</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>赤水河</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434836/index.html</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>鄂豫皖革命根据地</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>金沙江</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>钓鱼岛</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>阜平县</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434778/index.html</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>陕北</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>陕甘宁边区</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>陕西省</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434796/index.html</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>雁门关</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>香港岛</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>鸭绿江</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434816/index.html</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>黄浦江</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434715/index.html</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434732/index.html</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/excel/location.xlsx
+++ b/data/excel/location.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E237"/>
+  <dimension ref="A1:E272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,7 +2168,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>乌兹别克斯坦</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2185,7 +2185,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>亚丁港</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>亚丁湾</t>
+          <t>亚丁港</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2219,14 +2219,14 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>亚太地区</t>
+          <t>亚丁湾</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434761/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2236,14 +2236,14 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>亚洲地区</t>
+          <t>亚太地区</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434716/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434761/index.html</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2253,14 +2253,14 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>伏牛山</t>
+          <t>亚洲地区</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434700/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434716/index.html</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2270,14 +2270,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>俄国</t>
+          <t>伏牛山</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434845/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434700/index.html</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2287,14 +2287,14 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>兰州</t>
+          <t>俄国</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434718/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434845/index.html</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2304,7 +2304,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>俄罗斯</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2321,14 +2321,14 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>兰州</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434696/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434718/index.html</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2338,7 +2338,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>凤阳县</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -2355,14 +2355,14 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434696/index.html</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2372,7 +2372,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>北戴河</t>
+          <t>凤阳县</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -2389,7 +2389,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>北运河</t>
+          <t>利比亚</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -2406,7 +2406,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -2423,14 +2423,14 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>匈牙利</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434833/index.html</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2440,14 +2440,14 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>华中地区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434837/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2457,7 +2457,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>北戴河</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2474,7 +2474,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>华北地区</t>
+          <t>北运河</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -2508,14 +2508,14 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>华盛顿</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434838/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -2525,14 +2525,14 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>南京长江大桥</t>
+          <t>华中地区</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434837/index.html</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -2542,7 +2542,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>南沙群岛</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -2559,14 +2559,14 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>南浦大桥</t>
+          <t>华北地区</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434806/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -2576,7 +2576,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>南运河</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2593,14 +2593,14 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>南通</t>
+          <t>华盛顿</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434838/index.html</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -2610,7 +2610,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>南京长江大桥</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -2627,7 +2627,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>台湾</t>
+          <t>南沙群岛</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2644,14 +2644,14 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>台湾地区</t>
+          <t>南浦大桥</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434806/index.html</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -2661,14 +2661,14 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>南运河</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434732/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -2678,14 +2678,14 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>哈尔滨</t>
+          <t>南通</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434665/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -2695,7 +2695,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>南非</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -2712,14 +2712,14 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434791/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -2729,7 +2729,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>大中城市</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -2746,7 +2746,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>大城市</t>
+          <t>台湾</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>大清河</t>
+          <t>台湾地区</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -2780,14 +2780,14 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>大渡河</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434732/index.html</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -2797,14 +2797,14 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>哈尔滨</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434811/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434665/index.html</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -2814,7 +2814,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>太原</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -2831,14 +2831,14 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>太平洋地区</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434847/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434791/index.html</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -2848,14 +2848,14 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>夹金山</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434636/index.html</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -2865,7 +2865,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>子牙河</t>
+          <t>坦桑尼亚</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -2882,14 +2882,14 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>宁三省</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434687/index.html</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -2899,14 +2899,14 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>宁冈县</t>
+          <t>大中城市</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434545/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -2916,7 +2916,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>大城市</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -2933,7 +2933,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>宁夏回族自治区</t>
+          <t>大清河</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -2950,14 +2950,14 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>宁都县</t>
+          <t>大渡河</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434832/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -2967,14 +2967,14 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434811/index.html</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -2984,7 +2984,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>太原</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -3001,14 +3001,14 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>太平洋地区</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434847/index.html</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3018,14 +3018,14 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>山海关</t>
+          <t>夹金山</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434834/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -3035,7 +3035,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>子牙河</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>山西省</t>
+          <t>宁三省</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -3069,14 +3069,14 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>巴黎</t>
+          <t>宁冈县</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434545/index.html</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3086,7 +3086,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -3103,14 +3103,14 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>宁夏回族自治区</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434733/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -3120,14 +3120,14 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>宁都县</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434832/index.html</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3137,7 +3137,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -3154,14 +3154,14 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>德国</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434809/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -3171,14 +3171,14 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434738/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -3188,14 +3188,14 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>文明城市</t>
+          <t>山海关</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434834/index.html</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -3205,7 +3205,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>新安江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -3222,7 +3222,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>新泽西州</t>
+          <t>山西省</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -3239,7 +3239,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>巴基斯坦</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -3256,7 +3256,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -3273,7 +3273,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>无锡</t>
+          <t>巴黎</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -3290,14 +3290,14 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>日内瓦</t>
+          <t>希腊</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434735/index.html</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -3307,7 +3307,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -3324,14 +3324,14 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>旧金山</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434733/index.html</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -3341,7 +3341,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -3358,7 +3358,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>晋察冀边区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -3375,14 +3375,14 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>朝鲜</t>
+          <t>德国</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434809/index.html</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -3392,7 +3392,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -3409,14 +3409,14 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>武昌</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434738/index.html</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -3426,7 +3426,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>武汉三镇</t>
+          <t>挪威</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -3443,14 +3443,14 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>文明城市</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434805/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -3460,7 +3460,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>武汉长江大桥</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -3477,7 +3477,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>永兴岛</t>
+          <t>新安江</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -3494,14 +3494,14 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>永和市</t>
+          <t>新泽西州</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434658/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -3511,7 +3511,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>永定河</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -3528,14 +3528,14 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>汉阳</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434829/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -3545,7 +3545,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>江南</t>
+          <t>新西兰</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -3562,7 +3562,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>无锡</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -3579,7 +3579,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>日内瓦</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -3596,7 +3596,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -3613,14 +3613,14 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>江西省</t>
+          <t>旧金山</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434832/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -3630,7 +3630,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>沈阳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -3647,7 +3647,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>晋察冀边区</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -3664,14 +3664,14 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>河北省</t>
+          <t>智利</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434798/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434802/index.html</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -3681,7 +3681,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>朝鲜</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -3698,7 +3698,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>法国</t>
+          <t>柬埔寨</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -3732,7 +3732,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>泸定桥</t>
+          <t>武昌</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -3749,7 +3749,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>洛阳</t>
+          <t>武汉三镇</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -3766,14 +3766,14 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>济南</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434805/index.html</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -3783,7 +3783,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>武汉长江大桥</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -3800,14 +3800,14 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>比利时</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434835/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434779/index.html</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -3817,7 +3817,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>永兴岛</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -3834,14 +3834,14 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>海南岛</t>
+          <t>永和市</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434658/index.html</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -3851,7 +3851,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>海南省</t>
+          <t>永定河</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -3868,14 +3868,14 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>清川江</t>
+          <t>汉阳</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434567/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434829/index.html</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -3885,7 +3885,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>湄公河</t>
+          <t>江南</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -3902,7 +3902,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -3919,14 +3919,14 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -3936,7 +3936,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -3953,14 +3953,14 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>湖南省</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434781/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434832/index.html</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -3970,14 +3970,14 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>滨海新区</t>
+          <t>沈阳</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434721/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -3987,7 +3987,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>澎湖列岛</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -4004,14 +4004,14 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>澜沧江</t>
+          <t>河北省</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434798/index.html</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -4021,7 +4021,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>澳门</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -4038,7 +4038,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>澳门特别行政区</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -4055,14 +4055,14 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>珠海市</t>
+          <t>法国</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434711/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -4072,14 +4072,14 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434847/index.html</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -4089,14 +4089,14 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434733/index.html</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -4106,7 +4106,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>泸定桥</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -4123,14 +4123,14 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>洛阳</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434711/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -4140,7 +4140,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>济南</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -4157,7 +4157,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -4174,14 +4174,14 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>苏州工业园区</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434835/index.html</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -4191,14 +4191,14 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434797/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -4208,7 +4208,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>苏联</t>
+          <t>海南岛</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -4225,14 +4225,14 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>海南省</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434820/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -4242,14 +4242,14 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>西北</t>
+          <t>清川江</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434567/index.html</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -4259,14 +4259,14 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>西北地区</t>
+          <t>湄公河</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434727/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -4276,7 +4276,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -4293,14 +4293,14 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>西南地区</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434555/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -4310,7 +4310,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>西宁</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -4327,14 +4327,14 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>西沙群岛</t>
+          <t>湖南省</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434781/index.html</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -4344,14 +4344,14 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>滨海新区</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434721/index.html</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -4361,7 +4361,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>西藏自治区</t>
+          <t>澎湖列岛</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -4378,7 +4378,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>澜沧江</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -4395,7 +4395,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>贵阳</t>
+          <t>澳大利亚</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -4412,14 +4412,14 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>赤水河</t>
+          <t>澳门</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434836/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -4429,14 +4429,14 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>澳门特别行政区</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -4446,14 +4446,14 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>珠海市</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434711/index.html</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -4463,14 +4463,14 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>郑州</t>
+          <t>瑞典</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434736/index.html</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -4480,7 +4480,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>鄂豫皖革命根据地</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -4497,7 +4497,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -4514,7 +4514,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>金沙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -4531,14 +4531,14 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>钓鱼岛</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434711/index.html</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -4548,7 +4548,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>长春</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -4565,14 +4565,14 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>阜平县</t>
+          <t>罗马尼亚</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434778/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434736/index.html</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -4582,7 +4582,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>陕北</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -4599,14 +4599,14 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>陕甘宁边区</t>
+          <t>芬兰</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434845/index.html</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -4616,7 +4616,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -4633,14 +4633,14 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>陕西省</t>
+          <t>苏州工业园区</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434796/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -4650,14 +4650,14 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>雁门关</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434797/index.html</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -4667,7 +4667,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>青岛</t>
+          <t>苏联</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -4684,14 +4684,14 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>英国</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434820/index.html</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -4701,7 +4701,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>香港</t>
+          <t>荷兰</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -4718,14 +4718,14 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>香港岛</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434832/index.html</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -4735,14 +4735,14 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>鸭绿江</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434816/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -4752,14 +4752,14 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>黄浦江</t>
+          <t>西北</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434715/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -4769,17 +4769,612 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>西北地区</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434727/index.html</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>西南</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>西南地区</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434555/index.html</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>西沙群岛</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434758/index.html</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>西藏自治区</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>赞比亚</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>赤水河</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434836/index.html</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>鄂豫皖革命根据地</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>金沙江</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>钓鱼岛</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>阜平县</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434778/index.html</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>阿尔及利亚</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>陕北</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>陕甘宁边区</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>陕西省</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434796/index.html</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>雁门关</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>韩国</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>香港岛</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>马来西亚</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>鸭绿江</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434816/index.html</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>黄浦江</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434715/index.html</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
           <t>https://www.dswxyjy.org.cn/GB/434461/434465/434732/index.html</t>
         </is>
       </c>
-      <c r="E237" t="n">
+      <c r="E272" t="n">
         <v>0</v>
       </c>
     </row>
